--- a/Conditional Formatting Excel Tutorial File.xlsx
+++ b/Conditional Formatting Excel Tutorial File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\OneDrive\Desktop\excel-conditional-formatting-lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE12AABD-2C2A-4D60-B298-E861FD33474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26287748-6693-4EEF-B092-D337EF1C6F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -333,7 +333,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -347,9 +358,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -387,7 +398,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -493,7 +504,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -635,7 +646,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -644,22 +655,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1027015F-D30F-450C-928C-DE78480974B7}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -729,7 +740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -764,7 +775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -799,7 +810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -834,7 +845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -869,7 +880,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -904,7 +915,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -939,7 +950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -974,7 +985,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1009,19 +1020,22 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D22" t="str">
         <f t="shared" ref="D22:D23" si="0">CONCATENATE(B12," ",C12)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1029,12 +1043,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CCAA7F-6F85-4102-B7D4-D80770622F9F}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="10.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>72</v>
       </c>
@@ -1072,7 +1086,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1113,7 +1127,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1154,7 +1168,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -1196,6 +1210,15 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:M2">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Conditional Formatting Excel Tutorial File.xlsx
+++ b/Conditional Formatting Excel Tutorial File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\OneDrive\Desktop\excel-conditional-formatting-lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26287748-6693-4EEF-B092-D337EF1C6F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AB76A1-9774-4726-92DF-2F453527D1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -333,14 +333,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1033,8 +1060,29 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="aboveAverage" dxfId="2" priority="6"/>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 H11:H1048576">
+    <cfRule type="aboveAverage" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H10">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>H2:H10&gt;50000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>E2:E10&gt;30</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
